--- a/docs/sample-multi-section-workbook.xlsx
+++ b/docs/sample-multi-section-workbook.xlsx
@@ -142,10 +142,10 @@
       <c r="A3" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="n" s="0">
+      <c r="B3" t="n">
         <v>120.0</v>
       </c>
-      <c r="C3" t="n" s="0">
+      <c r="C3" t="n">
         <v>1.2E7</v>
       </c>
     </row>
@@ -153,10 +153,10 @@
       <c r="A4" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B4" t="n" s="0">
+      <c r="B4" t="n">
         <v>80.0</v>
       </c>
-      <c r="C4" t="n" s="0">
+      <c r="C4" t="n">
         <v>6400000.0</v>
       </c>
     </row>
@@ -164,10 +164,10 @@
       <c r="A5" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B5" t="n" s="0">
+      <c r="B5" t="n">
         <v>30.0</v>
       </c>
-      <c r="C5" t="n" s="0">
+      <c r="C5" t="n">
         <v>2250000.0</v>
       </c>
     </row>

--- a/docs/sample-multi-section-workbook.xlsx
+++ b/docs/sample-multi-section-workbook.xlsx
@@ -142,10 +142,10 @@
       <c r="A3" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="n" s="0">
         <v>120.0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="n" s="0">
         <v>1.2E7</v>
       </c>
     </row>
@@ -153,10 +153,10 @@
       <c r="A4" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="n" s="0">
         <v>80.0</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="n" s="0">
         <v>6400000.0</v>
       </c>
     </row>
@@ -164,10 +164,10 @@
       <c r="A5" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="n" s="0">
         <v>30.0</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="n" s="0">
         <v>2250000.0</v>
       </c>
     </row>

--- a/docs/sample-multi-section-workbook.xlsx
+++ b/docs/sample-multi-section-workbook.xlsx
@@ -29,31 +29,31 @@
     <t>Marketing</t>
   </si>
   <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
     <t>E001</t>
   </si>
   <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Johnson</t>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Bob</t>
   </si>
   <si>
     <t>E002</t>
   </si>
   <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Smith</t>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Carol</t>
   </si>
   <si>
     <t>E003</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Williams</t>
   </si>
   <si>
     <t>2025 Comprehensive Analysis</t>
@@ -142,10 +142,10 @@
       <c r="A3" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="n" s="0">
+      <c r="B3" t="n">
         <v>120.0</v>
       </c>
-      <c r="C3" t="n" s="0">
+      <c r="C3" t="n">
         <v>1.2E7</v>
       </c>
     </row>
@@ -153,10 +153,10 @@
       <c r="A4" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B4" t="n" s="0">
+      <c r="B4" t="n">
         <v>80.0</v>
       </c>
-      <c r="C4" t="n" s="0">
+      <c r="C4" t="n">
         <v>6400000.0</v>
       </c>
     </row>
@@ -164,10 +164,10 @@
       <c r="A5" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B5" t="n" s="0">
+      <c r="B5" t="n">
         <v>30.0</v>
       </c>
-      <c r="C5" t="n" s="0">
+      <c r="C5" t="n">
         <v>2250000.0</v>
       </c>
     </row>
@@ -231,52 +231,52 @@
     <row r="3"/>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" t="n" s="0">
+      <c r="E4" t="n">
         <v>145000.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>2</v>
       </c>
-      <c r="E5" t="n" s="0">
+      <c r="E5" t="n">
         <v>95000.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s">
         <v>3</v>
       </c>
-      <c r="E6" t="n" s="0">
+      <c r="E6" t="n">
         <v>85000.0</v>
       </c>
     </row>

--- a/docs/sample-multi-section-workbook.xlsx
+++ b/docs/sample-multi-section-workbook.xlsx
@@ -29,31 +29,31 @@
     <t>Marketing</t>
   </si>
   <si>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
     <t>Johnson</t>
   </si>
   <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>E001</t>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>Bob</t>
   </si>
   <si>
     <t>Smith</t>
   </si>
   <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>E002</t>
+    <t>E003</t>
+  </si>
+  <si>
+    <t>Carol</t>
   </si>
   <si>
     <t>Williams</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>E003</t>
   </si>
   <si>
     <t>2025 Comprehensive Analysis</t>
@@ -142,10 +142,10 @@
       <c r="A3" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="n" s="0">
         <v>120.0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="n" s="0">
         <v>1.2E7</v>
       </c>
     </row>
@@ -153,10 +153,10 @@
       <c r="A4" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="n" s="0">
         <v>80.0</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="n" s="0">
         <v>6400000.0</v>
       </c>
     </row>
@@ -164,10 +164,10 @@
       <c r="A5" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="n" s="0">
         <v>30.0</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="n" s="0">
         <v>2250000.0</v>
       </c>
     </row>
@@ -231,13 +231,13 @@
     <row r="3"/>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -248,13 +248,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
@@ -265,13 +265,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>

--- a/docs/sample-multi-section-workbook.xlsx
+++ b/docs/sample-multi-section-workbook.xlsx
@@ -29,31 +29,31 @@
     <t>Marketing</t>
   </si>
   <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
     <t>E001</t>
   </si>
   <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Johnson</t>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Bob</t>
   </si>
   <si>
     <t>E002</t>
   </si>
   <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Smith</t>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Carol</t>
   </si>
   <si>
     <t>E003</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Williams</t>
   </si>
   <si>
     <t>2025 Comprehensive Analysis</t>
@@ -142,10 +142,10 @@
       <c r="A3" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B3" t="n" s="0">
+      <c r="B3" t="n">
         <v>120.0</v>
       </c>
-      <c r="C3" t="n" s="0">
+      <c r="C3" t="n">
         <v>1.2E7</v>
       </c>
     </row>
@@ -153,10 +153,10 @@
       <c r="A4" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B4" t="n" s="0">
+      <c r="B4" t="n">
         <v>80.0</v>
       </c>
-      <c r="C4" t="n" s="0">
+      <c r="C4" t="n">
         <v>6400000.0</v>
       </c>
     </row>
@@ -164,10 +164,10 @@
       <c r="A5" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B5" t="n" s="0">
+      <c r="B5" t="n">
         <v>30.0</v>
       </c>
-      <c r="C5" t="n" s="0">
+      <c r="C5" t="n">
         <v>2250000.0</v>
       </c>
     </row>
@@ -231,13 +231,13 @@
     <row r="3"/>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -248,13 +248,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
@@ -265,13 +265,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
